--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="35">
   <si>
     <t>configuracion</t>
   </si>
@@ -573,10 +573,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L2" t="s">
         <v>28</v>
@@ -638,10 +644,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
       <c r="L3" t="s">
         <v>27</v>
@@ -703,10 +715,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
       <c r="L4" t="s">
         <v>28</v>
@@ -768,10 +786,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5" t="s">
         <v>33</v>
@@ -833,10 +857,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L6" t="s">
         <v>28</v>
@@ -898,10 +928,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L7" t="s">
         <v>28</v>
@@ -963,10 +999,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
       </c>
       <c r="L8" t="s">
         <v>28</v>
@@ -1028,11 +1070,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
       </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
       <c r="L9" t="s">
         <v>28</v>
       </c>
@@ -1061,7 +1109,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1093,10 +1141,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
       </c>
       <c r="L10" t="s">
         <v>29</v>
@@ -1158,10 +1212,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
       </c>
       <c r="L11" t="s">
         <v>28</v>
@@ -1223,10 +1283,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
       </c>
       <c r="L12" t="s">
         <v>28</v>
@@ -1288,10 +1354,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
       </c>
       <c r="L13" t="s">
         <v>33</v>
@@ -1353,10 +1425,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H14">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L14" t="s">
         <v>28</v>
@@ -1418,10 +1496,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H15">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
       </c>
       <c r="L15" t="s">
         <v>28</v>
@@ -1483,10 +1567,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H16">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
       </c>
       <c r="L16" t="s">
         <v>28</v>
@@ -1548,10 +1638,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H17">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
       </c>
       <c r="L17" t="s">
         <v>33</v>
@@ -1613,10 +1709,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H18">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
       </c>
       <c r="L18" t="s">
         <v>28</v>
@@ -1678,10 +1780,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H19">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L19" t="s">
         <v>28</v>
@@ -1743,10 +1851,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H20">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L20" t="s">
         <v>28</v>
@@ -1808,10 +1922,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H21">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="s">
         <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
       </c>
       <c r="L21" t="s">
         <v>28</v>
@@ -1873,10 +1993,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H22">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>28</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
       </c>
       <c r="L22" t="s">
         <v>28</v>
@@ -1938,10 +2064,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H23">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
+      </c>
+      <c r="J23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
       </c>
       <c r="L23" t="s">
         <v>28</v>
@@ -2003,10 +2135,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H24">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I24" t="s">
         <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L24" t="s">
         <v>28</v>
@@ -2068,10 +2206,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
       </c>
       <c r="L25" t="s">
         <v>28</v>
@@ -2133,10 +2277,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H26">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
       </c>
       <c r="L26" t="s">
         <v>33</v>
@@ -2198,10 +2348,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H27">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L27" t="s">
         <v>28</v>
@@ -2263,10 +2419,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H28">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
+      </c>
+      <c r="J28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
@@ -2328,10 +2490,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H29">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L29" t="s">
         <v>28</v>
@@ -2393,10 +2561,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H30">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2458,10 +2632,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H31">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>28</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
       </c>
       <c r="L31" t="s">
         <v>28</v>
@@ -2523,10 +2703,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H32">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>28</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
       </c>
       <c r="L32" t="s">
         <v>28</v>
@@ -2588,10 +2774,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H33">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
       </c>
       <c r="L33" t="s">
         <v>28</v>
@@ -2653,11 +2845,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H34">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
       </c>
+      <c r="J34" t="s">
+        <v>28</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
       <c r="L34" t="s">
         <v>28</v>
       </c>
@@ -2686,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -2718,10 +2916,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H35">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L35" t="s">
         <v>28</v>
@@ -2783,10 +2987,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H36">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="s">
         <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>28</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
       </c>
       <c r="L36" t="s">
         <v>34</v>
@@ -2848,10 +3058,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H37">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
       </c>
       <c r="L37" t="s">
         <v>33</v>
@@ -2913,10 +3129,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H38">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="s">
         <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>28</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
       </c>
       <c r="L38" t="s">
         <v>28</v>
@@ -2978,10 +3200,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H39">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
       </c>
       <c r="L39" t="s">
         <v>32</v>
@@ -3043,10 +3271,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H40">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
+      </c>
+      <c r="J40" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
       </c>
       <c r="L40" t="s">
         <v>28</v>
@@ -3108,10 +3342,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H41">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>27</v>
+      </c>
+      <c r="K41">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L41" t="s">
         <v>28</v>
@@ -3173,10 +3413,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H42">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I42" t="s">
         <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>28</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
       </c>
       <c r="L42" t="s">
         <v>28</v>
@@ -3238,10 +3484,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H43">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>28</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
       </c>
       <c r="L43" t="s">
         <v>28</v>
@@ -3303,10 +3555,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H44">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I44" t="s">
         <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>28</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
       </c>
       <c r="L44" t="s">
         <v>28</v>
@@ -3368,10 +3626,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H45">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>28</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
       </c>
       <c r="L45" t="s">
         <v>28</v>
@@ -3433,10 +3697,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H46">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I46" t="s">
         <v>15</v>
+      </c>
+      <c r="J46" t="s">
+        <v>28</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
       </c>
       <c r="L46" t="s">
         <v>33</v>
@@ -3498,10 +3768,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H47">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I47" t="s">
         <v>15</v>
+      </c>
+      <c r="J47" t="s">
+        <v>28</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3563,10 +3839,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H48">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
+      </c>
+      <c r="J48" t="s">
+        <v>28</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -3628,11 +3910,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H49">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
       </c>
+      <c r="J49" t="s">
+        <v>28</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
       <c r="L49" t="s">
         <v>28</v>
       </c>
@@ -3661,7 +3949,7 @@
         <v>7</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49">
         <v>7</v>
@@ -3693,11 +3981,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H50">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I50" t="s">
         <v>15</v>
       </c>
+      <c r="J50" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
       <c r="L50" t="s">
         <v>28</v>
       </c>
@@ -3726,7 +4020,7 @@
         <v>7</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V50">
         <v>7</v>
@@ -3758,10 +4052,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H51">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I51" t="s">
         <v>15</v>
+      </c>
+      <c r="J51" t="s">
+        <v>28</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
       </c>
       <c r="L51" t="s">
         <v>28</v>
@@ -3823,10 +4123,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H52">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>28</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
       </c>
       <c r="L52" t="s">
         <v>28</v>
@@ -3888,10 +4194,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H53">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>28</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
       </c>
       <c r="L53" t="s">
         <v>28</v>
@@ -3953,10 +4265,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H54">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I54" t="s">
         <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L54" t="s">
         <v>28</v>
@@ -4018,10 +4336,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H55">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I55" t="s">
         <v>15</v>
+      </c>
+      <c r="J55" t="s">
+        <v>30</v>
+      </c>
+      <c r="K55">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L55" t="s">
         <v>28</v>
@@ -4083,10 +4407,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H56">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I56" t="s">
         <v>15</v>
+      </c>
+      <c r="J56" t="s">
+        <v>28</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
       </c>
       <c r="L56" t="s">
         <v>33</v>
@@ -4148,10 +4478,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H57">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="s">
         <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>28</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
       </c>
       <c r="L57" t="s">
         <v>28</v>
@@ -4213,10 +4549,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H58">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I58" t="s">
         <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>27</v>
+      </c>
+      <c r="K58">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L58" t="s">
         <v>34</v>
@@ -4278,10 +4620,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H59">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I59" t="s">
         <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>28</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
       </c>
       <c r="L59" t="s">
         <v>33</v>
@@ -4343,10 +4691,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H60">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I60" t="s">
         <v>15</v>
+      </c>
+      <c r="J60" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L60" t="s">
         <v>28</v>
@@ -4408,11 +4762,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H61">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I61" t="s">
         <v>15</v>
       </c>
+      <c r="J61" t="s">
+        <v>28</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
       <c r="L61" t="s">
         <v>28</v>
       </c>
@@ -4441,7 +4801,7 @@
         <v>7</v>
       </c>
       <c r="U61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61">
         <v>7</v>
@@ -4473,10 +4833,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H62">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
+      </c>
+      <c r="J62" t="s">
+        <v>28</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
       </c>
       <c r="L62" t="s">
         <v>33</v>
@@ -4538,10 +4904,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H63">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I63" t="s">
         <v>15</v>
+      </c>
+      <c r="J63" t="s">
+        <v>28</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
       </c>
       <c r="L63" t="s">
         <v>28</v>
@@ -4603,10 +4975,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H64">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I64" t="s">
         <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>28</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
       </c>
       <c r="L64" t="s">
         <v>31</v>
@@ -4668,10 +5046,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H65">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="s">
         <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>28</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
       </c>
       <c r="L65" t="s">
         <v>28</v>
@@ -4733,10 +5117,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H66">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="s">
         <v>15</v>
+      </c>
+      <c r="J66" t="s">
+        <v>28</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
       </c>
       <c r="L66" t="s">
         <v>28</v>
@@ -4798,10 +5188,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H67">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I67" t="s">
         <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>28</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
       </c>
       <c r="L67" t="s">
         <v>28</v>
@@ -4863,10 +5259,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H68">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I68" t="s">
         <v>15</v>
+      </c>
+      <c r="J68" t="s">
+        <v>30</v>
+      </c>
+      <c r="K68">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L68" t="s">
         <v>28</v>
@@ -4928,10 +5330,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H69">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
+      </c>
+      <c r="J69" t="s">
+        <v>28</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
       </c>
       <c r="L69" t="s">
         <v>33</v>
@@ -4993,11 +5401,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H70">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
       </c>
+      <c r="J70" t="s">
+        <v>28</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
       <c r="L70" t="s">
         <v>28</v>
       </c>
@@ -5026,7 +5440,7 @@
         <v>7</v>
       </c>
       <c r="U70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V70">
         <v>7</v>
@@ -5058,10 +5472,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H71">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I71" t="s">
         <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>28</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
       </c>
       <c r="L71" t="s">
         <v>28</v>
@@ -5123,10 +5543,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H72">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
+      </c>
+      <c r="J72" t="s">
+        <v>28</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
       </c>
       <c r="L72" t="s">
         <v>28</v>
@@ -5188,10 +5614,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H73">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="s">
         <v>15</v>
+      </c>
+      <c r="J73" t="s">
+        <v>28</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
       </c>
       <c r="L73" t="s">
         <v>28</v>
@@ -5253,10 +5685,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H74">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I74" t="s">
         <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>28</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
       </c>
       <c r="L74" t="s">
         <v>28</v>
@@ -5318,11 +5756,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H75">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
       </c>
+      <c r="J75" t="s">
+        <v>33</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
       <c r="L75" t="s">
         <v>28</v>
       </c>
@@ -5339,7 +5783,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -5383,10 +5827,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H76">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
+      </c>
+      <c r="J76" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
       </c>
       <c r="L76" t="s">
         <v>28</v>
@@ -5448,10 +5898,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H77">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I77" t="s">
         <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>28</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
       </c>
       <c r="L77" t="s">
         <v>28</v>
@@ -5513,11 +5969,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H78">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I78" t="s">
         <v>15</v>
       </c>
+      <c r="J78" t="s">
+        <v>28</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
       <c r="L78" t="s">
         <v>28</v>
       </c>
@@ -5546,7 +6008,7 @@
         <v>7</v>
       </c>
       <c r="U78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V78">
         <v>7</v>
@@ -5578,10 +6040,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H79">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I79" t="s">
         <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>28</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
       </c>
       <c r="L79" t="s">
         <v>28</v>
@@ -5643,10 +6111,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H80">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I80" t="s">
         <v>15</v>
+      </c>
+      <c r="J80" t="s">
+        <v>32</v>
+      </c>
+      <c r="K80">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L80" t="s">
         <v>33</v>
@@ -5708,10 +6182,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H81">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>28</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
       </c>
       <c r="L81" t="s">
         <v>28</v>
@@ -5773,10 +6253,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H82">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>27</v>
+      </c>
+      <c r="K82">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L82" t="s">
         <v>28</v>
@@ -5838,10 +6324,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H83">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I83" t="s">
         <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>32</v>
+      </c>
+      <c r="K83">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L83" t="s">
         <v>28</v>
@@ -5903,10 +6395,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H84">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>28</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
       </c>
       <c r="L84" t="s">
         <v>32</v>
@@ -5968,10 +6466,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H85">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>
+      </c>
+      <c r="J85" t="s">
+        <v>28</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
       </c>
       <c r="L85" t="s">
         <v>34</v>
@@ -6033,10 +6537,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H86">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I86" t="s">
         <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>27</v>
+      </c>
+      <c r="K86">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L86" t="s">
         <v>28</v>
@@ -6098,10 +6608,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
+      </c>
+      <c r="J87" t="s">
+        <v>31</v>
+      </c>
+      <c r="K87">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L87" t="s">
         <v>28</v>
@@ -6163,10 +6679,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H88">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="s">
         <v>15</v>
+      </c>
+      <c r="J88" t="s">
+        <v>28</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
       </c>
       <c r="L88" t="s">
         <v>28</v>
@@ -6228,10 +6750,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H89">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I89" t="s">
         <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>28</v>
+      </c>
+      <c r="K89">
+        <v>1</v>
       </c>
       <c r="L89" t="s">
         <v>28</v>
@@ -6293,10 +6821,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H90">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I90" t="s">
         <v>15</v>
+      </c>
+      <c r="J90" t="s">
+        <v>34</v>
+      </c>
+      <c r="K90">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L90" t="s">
         <v>28</v>
@@ -6358,10 +6892,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H91">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I91" t="s">
         <v>15</v>
+      </c>
+      <c r="J91" t="s">
+        <v>28</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
       </c>
       <c r="L91" t="s">
         <v>28</v>
@@ -6423,10 +6963,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H92">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I92" t="s">
         <v>15</v>
+      </c>
+      <c r="J92" t="s">
+        <v>28</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
       </c>
       <c r="L92" t="s">
         <v>28</v>
@@ -6488,10 +7034,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H93">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I93" t="s">
         <v>15</v>
+      </c>
+      <c r="J93" t="s">
+        <v>28</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
       </c>
       <c r="L93" t="s">
         <v>27</v>
@@ -6553,11 +7105,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H94">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I94" t="s">
         <v>15</v>
       </c>
+      <c r="J94" t="s">
+        <v>28</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
       <c r="L94" t="s">
         <v>28</v>
       </c>
@@ -6586,7 +7144,7 @@
         <v>7</v>
       </c>
       <c r="U94">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V94">
         <v>7</v>
@@ -6618,10 +7176,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H95">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I95" t="s">
         <v>15</v>
+      </c>
+      <c r="J95" t="s">
+        <v>28</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
       </c>
       <c r="L95" t="s">
         <v>27</v>
@@ -6683,10 +7247,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H96">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I96" t="s">
         <v>15</v>
+      </c>
+      <c r="J96" t="s">
+        <v>28</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
       </c>
       <c r="L96" t="s">
         <v>32</v>
@@ -6748,10 +7318,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H97">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I97" t="s">
         <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>28</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
       </c>
       <c r="L97" t="s">
         <v>28</v>
@@ -6813,10 +7389,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H98">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
+      </c>
+      <c r="J98" t="s">
+        <v>32</v>
+      </c>
+      <c r="K98">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L98" t="s">
         <v>28</v>
@@ -6878,10 +7460,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H99">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
+      </c>
+      <c r="J99" t="s">
+        <v>28</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
       </c>
       <c r="L99" t="s">
         <v>28</v>
@@ -6943,11 +7531,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H100">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I100" t="s">
         <v>15</v>
       </c>
+      <c r="J100" t="s">
+        <v>28</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
       <c r="L100" t="s">
         <v>28</v>
       </c>
@@ -6976,7 +7570,7 @@
         <v>7</v>
       </c>
       <c r="U100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V100">
         <v>7</v>
@@ -7008,10 +7602,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H101">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I101" t="s">
         <v>15</v>
+      </c>
+      <c r="J101" t="s">
+        <v>28</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
       </c>
       <c r="L101" t="s">
         <v>28</v>
@@ -7073,10 +7673,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H102">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I102" t="s">
         <v>15</v>
+      </c>
+      <c r="J102" t="s">
+        <v>28</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
       </c>
       <c r="L102" t="s">
         <v>28</v>
@@ -7138,10 +7744,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H103">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
+      </c>
+      <c r="J103" t="s">
+        <v>28</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
       </c>
       <c r="L103" t="s">
         <v>28</v>
@@ -7203,10 +7815,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H104">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I104" t="s">
         <v>15</v>
+      </c>
+      <c r="J104" t="s">
+        <v>28</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
       </c>
       <c r="L104" t="s">
         <v>32</v>
@@ -7268,10 +7886,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H105">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I105" t="s">
         <v>15</v>
+      </c>
+      <c r="J105" t="s">
+        <v>28</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
       </c>
       <c r="L105" t="s">
         <v>28</v>
@@ -7333,10 +7957,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H106">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I106" t="s">
         <v>15</v>
+      </c>
+      <c r="J106" t="s">
+        <v>28</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
       </c>
       <c r="L106" t="s">
         <v>28</v>
@@ -7398,10 +8028,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H107">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I107" t="s">
         <v>15</v>
+      </c>
+      <c r="J107" t="s">
+        <v>28</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
       </c>
       <c r="L107" t="s">
         <v>28</v>
@@ -7463,10 +8099,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H108">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I108" t="s">
         <v>15</v>
+      </c>
+      <c r="J108" t="s">
+        <v>28</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
       </c>
       <c r="L108" t="s">
         <v>28</v>
@@ -7528,10 +8170,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H109">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I109" t="s">
         <v>15</v>
+      </c>
+      <c r="J109" t="s">
+        <v>28</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
       </c>
       <c r="L109" t="s">
         <v>28</v>
@@ -7593,10 +8241,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H110">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I110" t="s">
         <v>15</v>
+      </c>
+      <c r="J110" t="s">
+        <v>28</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
       </c>
       <c r="L110" t="s">
         <v>28</v>
@@ -7658,10 +8312,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H111">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I111" t="s">
         <v>15</v>
+      </c>
+      <c r="J111" t="s">
+        <v>28</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
       </c>
       <c r="L111" t="s">
         <v>28</v>
@@ -7723,10 +8383,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H112">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I112" t="s">
         <v>15</v>
+      </c>
+      <c r="J112" t="s">
+        <v>28</v>
+      </c>
+      <c r="K112">
+        <v>1</v>
       </c>
       <c r="L112" t="s">
         <v>28</v>
@@ -7788,10 +8454,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H113">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I113" t="s">
         <v>15</v>
+      </c>
+      <c r="J113" t="s">
+        <v>29</v>
+      </c>
+      <c r="K113">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L113" t="s">
         <v>28</v>
@@ -7853,10 +8525,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H114">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I114" t="s">
         <v>15</v>
+      </c>
+      <c r="J114" t="s">
+        <v>28</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
       </c>
       <c r="L114" t="s">
         <v>28</v>
@@ -7918,10 +8596,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H115">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I115" t="s">
         <v>15</v>
+      </c>
+      <c r="J115" t="s">
+        <v>30</v>
+      </c>
+      <c r="K115">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L115" t="s">
         <v>33</v>
@@ -7983,10 +8667,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H116">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I116" t="s">
         <v>15</v>
+      </c>
+      <c r="J116" t="s">
+        <v>28</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
       </c>
       <c r="L116" t="s">
         <v>28</v>
@@ -8048,10 +8738,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H117">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="s">
         <v>15</v>
+      </c>
+      <c r="J117" t="s">
+        <v>28</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
       </c>
       <c r="L117" t="s">
         <v>28</v>
@@ -8113,10 +8809,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H118">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I118" t="s">
         <v>15</v>
+      </c>
+      <c r="J118" t="s">
+        <v>28</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
       </c>
       <c r="L118" t="s">
         <v>32</v>
@@ -8178,10 +8880,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H119">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I119" t="s">
         <v>15</v>
+      </c>
+      <c r="J119" t="s">
+        <v>28</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
       </c>
       <c r="L119" t="s">
         <v>32</v>
@@ -8243,10 +8951,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H120">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I120" t="s">
         <v>15</v>
+      </c>
+      <c r="J120" t="s">
+        <v>28</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
       </c>
       <c r="L120" t="s">
         <v>27</v>
@@ -8308,10 +9022,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H121">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I121" t="s">
         <v>15</v>
+      </c>
+      <c r="J121" t="s">
+        <v>34</v>
+      </c>
+      <c r="K121">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L121" t="s">
         <v>28</v>
@@ -8373,10 +9093,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H122">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I122" t="s">
         <v>15</v>
+      </c>
+      <c r="J122" t="s">
+        <v>29</v>
+      </c>
+      <c r="K122">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L122" t="s">
         <v>28</v>
@@ -8438,10 +9164,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H123">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I123" t="s">
         <v>15</v>
+      </c>
+      <c r="J123" t="s">
+        <v>28</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
       </c>
       <c r="L123" t="s">
         <v>28</v>
@@ -8503,10 +9235,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H124">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I124" t="s">
         <v>15</v>
+      </c>
+      <c r="J124" t="s">
+        <v>29</v>
+      </c>
+      <c r="K124">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L124" t="s">
         <v>28</v>
@@ -8568,10 +9306,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H125">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I125" t="s">
         <v>15</v>
+      </c>
+      <c r="J125" t="s">
+        <v>28</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
       </c>
       <c r="L125" t="s">
         <v>33</v>
@@ -8633,10 +9377,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H126">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I126" t="s">
         <v>15</v>
+      </c>
+      <c r="J126" t="s">
+        <v>34</v>
+      </c>
+      <c r="K126">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L126" t="s">
         <v>28</v>
@@ -8698,11 +9448,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H127">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I127" t="s">
         <v>15</v>
       </c>
+      <c r="J127" t="s">
+        <v>28</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
       <c r="L127" t="s">
         <v>28</v>
       </c>
@@ -8731,7 +9487,7 @@
         <v>7</v>
       </c>
       <c r="U127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V127">
         <v>7</v>
@@ -8763,10 +9519,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H128">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I128" t="s">
         <v>15</v>
+      </c>
+      <c r="J128" t="s">
+        <v>28</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
       </c>
       <c r="L128" t="s">
         <v>28</v>
@@ -8828,10 +9590,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H129">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I129" t="s">
         <v>15</v>
+      </c>
+      <c r="J129" t="s">
+        <v>28</v>
+      </c>
+      <c r="K129">
+        <v>1</v>
       </c>
       <c r="L129" t="s">
         <v>28</v>
@@ -8893,10 +9661,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H130">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I130" t="s">
         <v>15</v>
+      </c>
+      <c r="J130" t="s">
+        <v>28</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
       </c>
       <c r="L130" t="s">
         <v>28</v>
@@ -8958,10 +9732,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H131">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I131" t="s">
         <v>15</v>
+      </c>
+      <c r="J131" t="s">
+        <v>28</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
       </c>
       <c r="L131" t="s">
         <v>28</v>
@@ -9023,10 +9803,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H132">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I132" t="s">
         <v>15</v>
+      </c>
+      <c r="J132" t="s">
+        <v>28</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
       </c>
       <c r="L132" t="s">
         <v>29</v>
@@ -9088,10 +9874,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H133">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I133" t="s">
         <v>15</v>
+      </c>
+      <c r="J133" t="s">
+        <v>28</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
       </c>
       <c r="L133" t="s">
         <v>33</v>
@@ -9153,10 +9945,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H134">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I134" t="s">
         <v>15</v>
+      </c>
+      <c r="J134" t="s">
+        <v>28</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
       </c>
       <c r="L134" t="s">
         <v>28</v>
@@ -9218,10 +10016,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H135">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I135" t="s">
         <v>15</v>
+      </c>
+      <c r="J135" t="s">
+        <v>27</v>
+      </c>
+      <c r="K135">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L135" t="s">
         <v>28</v>
@@ -9283,10 +10087,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H136">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I136" t="s">
         <v>15</v>
+      </c>
+      <c r="J136" t="s">
+        <v>28</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
       </c>
       <c r="L136" t="s">
         <v>33</v>
@@ -9348,10 +10158,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H137">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I137" t="s">
         <v>15</v>
+      </c>
+      <c r="J137" t="s">
+        <v>30</v>
+      </c>
+      <c r="K137">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L137" t="s">
         <v>28</v>
@@ -9413,10 +10229,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H138">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I138" t="s">
         <v>15</v>
+      </c>
+      <c r="J138" t="s">
+        <v>28</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
       </c>
       <c r="L138" t="s">
         <v>31</v>
@@ -9478,10 +10300,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H139">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I139" t="s">
         <v>15</v>
+      </c>
+      <c r="J139" t="s">
+        <v>28</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
       </c>
       <c r="L139" t="s">
         <v>28</v>
@@ -9543,10 +10371,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H140">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I140" t="s">
         <v>15</v>
+      </c>
+      <c r="J140" t="s">
+        <v>30</v>
+      </c>
+      <c r="K140">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L140" t="s">
         <v>28</v>
@@ -9608,10 +10442,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H141">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I141" t="s">
         <v>15</v>
+      </c>
+      <c r="J141" t="s">
+        <v>28</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
       </c>
       <c r="L141" t="s">
         <v>34</v>
@@ -9661,7 +10501,7 @@
         <v>25</v>
       </c>
       <c r="D142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>7</v>
@@ -9673,11 +10513,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H142">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I142" t="s">
         <v>15</v>
       </c>
+      <c r="J142" t="s">
+        <v>33</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
       <c r="L142" t="s">
         <v>28</v>
       </c>
@@ -9694,7 +10540,7 @@
         <v>0</v>
       </c>
       <c r="Q142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R142" t="b">
         <v>1</v>
@@ -9738,10 +10584,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H143">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I143" t="s">
         <v>15</v>
+      </c>
+      <c r="J143" t="s">
+        <v>30</v>
+      </c>
+      <c r="K143">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L143" t="s">
         <v>33</v>
@@ -9803,11 +10655,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H144">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I144" t="s">
         <v>15</v>
       </c>
+      <c r="J144" t="s">
+        <v>33</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
       <c r="L144" t="s">
         <v>28</v>
       </c>
@@ -9824,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="Q144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R144" t="b">
         <v>1</v>
@@ -9868,10 +10726,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H145">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I145" t="s">
         <v>15</v>
+      </c>
+      <c r="J145" t="s">
+        <v>28</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
       </c>
       <c r="L145" t="s">
         <v>31</v>
@@ -9933,11 +10797,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H146">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I146" t="s">
         <v>15</v>
       </c>
+      <c r="J146" t="s">
+        <v>28</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
       <c r="L146" t="s">
         <v>28</v>
       </c>
@@ -9966,7 +10836,7 @@
         <v>7</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V146">
         <v>7</v>
@@ -9998,10 +10868,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H147">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I147" t="s">
         <v>15</v>
+      </c>
+      <c r="J147" t="s">
+        <v>28</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
       </c>
       <c r="L147" t="s">
         <v>33</v>
@@ -10063,11 +10939,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H148">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I148" t="s">
         <v>15</v>
       </c>
+      <c r="J148" t="s">
+        <v>28</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
       <c r="L148" t="s">
         <v>28</v>
       </c>
@@ -10096,7 +10978,7 @@
         <v>7</v>
       </c>
       <c r="U148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V148">
         <v>7</v>
@@ -10128,11 +11010,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H149">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I149" t="s">
         <v>15</v>
       </c>
+      <c r="J149" t="s">
+        <v>28</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
       <c r="L149" t="s">
         <v>28</v>
       </c>
@@ -10161,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V149">
         <v>7</v>
@@ -10193,10 +11081,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H150">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I150" t="s">
         <v>15</v>
+      </c>
+      <c r="J150" t="s">
+        <v>28</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
       </c>
       <c r="L150" t="s">
         <v>33</v>
@@ -10258,10 +11152,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H151">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I151" t="s">
         <v>15</v>
+      </c>
+      <c r="J151" t="s">
+        <v>30</v>
+      </c>
+      <c r="K151">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L151" t="s">
         <v>28</v>
@@ -10323,11 +11223,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H152">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I152" t="s">
         <v>15</v>
       </c>
+      <c r="J152" t="s">
+        <v>28</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
       <c r="L152" t="s">
         <v>28</v>
       </c>
@@ -10356,7 +11262,7 @@
         <v>7</v>
       </c>
       <c r="U152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V152">
         <v>7</v>
@@ -10388,10 +11294,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H153">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I153" t="s">
         <v>15</v>
+      </c>
+      <c r="J153" t="s">
+        <v>28</v>
+      </c>
+      <c r="K153">
+        <v>1</v>
       </c>
       <c r="L153" t="s">
         <v>30</v>
@@ -10453,10 +11365,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H154">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I154" t="s">
         <v>15</v>
+      </c>
+      <c r="J154" t="s">
+        <v>29</v>
+      </c>
+      <c r="K154">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L154" t="s">
         <v>28</v>
@@ -10518,10 +11436,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H155">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I155" t="s">
         <v>15</v>
+      </c>
+      <c r="J155" t="s">
+        <v>28</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
       </c>
       <c r="L155" t="s">
         <v>32</v>
@@ -10583,10 +11507,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H156">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I156" t="s">
         <v>15</v>
+      </c>
+      <c r="J156" t="s">
+        <v>28</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
       </c>
       <c r="L156" t="s">
         <v>28</v>
@@ -10648,10 +11578,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H157">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I157" t="s">
         <v>15</v>
+      </c>
+      <c r="J157" t="s">
+        <v>30</v>
+      </c>
+      <c r="K157">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L157" t="s">
         <v>28</v>
@@ -10713,10 +11649,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H158">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I158" t="s">
         <v>15</v>
+      </c>
+      <c r="J158" t="s">
+        <v>28</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
       </c>
       <c r="L158" t="s">
         <v>28</v>
@@ -10778,11 +11720,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H159">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I159" t="s">
         <v>15</v>
       </c>
+      <c r="J159" t="s">
+        <v>28</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
       <c r="L159" t="s">
         <v>28</v>
       </c>
@@ -10811,7 +11759,7 @@
         <v>7</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V159">
         <v>7</v>
@@ -10843,10 +11791,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H160">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I160" t="s">
         <v>15</v>
+      </c>
+      <c r="J160" t="s">
+        <v>28</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
       </c>
       <c r="L160" t="s">
         <v>32</v>
@@ -10908,10 +11862,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H161">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I161" t="s">
         <v>15</v>
+      </c>
+      <c r="J161" t="s">
+        <v>30</v>
+      </c>
+      <c r="K161">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L161" t="s">
         <v>28</v>
@@ -10973,11 +11933,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H162">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I162" t="s">
         <v>15</v>
       </c>
+      <c r="J162" t="s">
+        <v>28</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
       <c r="L162" t="s">
         <v>28</v>
       </c>
@@ -11006,7 +11972,7 @@
         <v>7</v>
       </c>
       <c r="U162">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V162">
         <v>7</v>
@@ -11038,10 +12004,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H163">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I163" t="s">
         <v>15</v>
+      </c>
+      <c r="J163" t="s">
+        <v>29</v>
+      </c>
+      <c r="K163">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L163" t="s">
         <v>33</v>
@@ -11103,10 +12075,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H164">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I164" t="s">
         <v>15</v>
+      </c>
+      <c r="J164" t="s">
+        <v>28</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
       </c>
       <c r="L164" t="s">
         <v>28</v>
@@ -11168,11 +12146,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H165">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I165" t="s">
         <v>15</v>
       </c>
+      <c r="J165" t="s">
+        <v>28</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
       <c r="L165" t="s">
         <v>28</v>
       </c>
@@ -11201,7 +12185,7 @@
         <v>7</v>
       </c>
       <c r="U165">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V165">
         <v>7</v>
@@ -11233,10 +12217,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H166">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I166" t="s">
         <v>15</v>
+      </c>
+      <c r="J166" t="s">
+        <v>27</v>
+      </c>
+      <c r="K166">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L166" t="s">
         <v>33</v>
@@ -11298,10 +12288,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H167">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I167" t="s">
         <v>15</v>
+      </c>
+      <c r="J167" t="s">
+        <v>28</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
       </c>
       <c r="L167" t="s">
         <v>28</v>
@@ -11363,11 +12359,17 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H168">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I168" t="s">
         <v>15</v>
       </c>
+      <c r="J168" t="s">
+        <v>28</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
       <c r="L168" t="s">
         <v>28</v>
       </c>
@@ -11396,7 +12398,7 @@
         <v>7</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V168">
         <v>7</v>
@@ -11428,10 +12430,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H169">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I169" t="s">
         <v>15</v>
+      </c>
+      <c r="J169" t="s">
+        <v>28</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
       </c>
       <c r="L169" t="s">
         <v>28</v>
@@ -11493,10 +12501,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H170">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I170" t="s">
         <v>15</v>
+      </c>
+      <c r="J170" t="s">
+        <v>30</v>
+      </c>
+      <c r="K170">
+        <v>0.8571428571428571</v>
       </c>
       <c r="L170" t="s">
         <v>28</v>
@@ -11558,10 +12572,16 @@
         <v>2.573841689777097</v>
       </c>
       <c r="H171">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I171" t="s">
         <v>15</v>
+      </c>
+      <c r="J171" t="s">
+        <v>28</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
       </c>
       <c r="L171" t="s">
         <v>28</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <v>7</v>
@@ -703,7 +703,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -745,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="b">
         <v>1</v>
@@ -754,7 +754,7 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -987,7 +987,7 @@
         <v>25</v>
       </c>
       <c r="D8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1058,7 +1058,7 @@
         <v>25</v>
       </c>
       <c r="D9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1100,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="b">
         <v>1</v>
@@ -1109,7 +1109,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1200,7 +1200,7 @@
         <v>25</v>
       </c>
       <c r="D11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1242,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="b">
         <v>1</v>
@@ -1251,7 +1251,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1271,7 +1271,7 @@
         <v>25</v>
       </c>
       <c r="D12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -1313,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="b">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1455,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="b">
         <v>1</v>
@@ -1484,7 +1484,7 @@
         <v>25</v>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1526,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="b">
         <v>1</v>
@@ -1535,7 +1535,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1555,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="D16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>7</v>
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="b">
         <v>1</v>
@@ -1697,7 +1697,7 @@
         <v>25</v>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="b">
         <v>1</v>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="b">
         <v>1</v>
@@ -1881,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -1910,7 +1910,7 @@
         <v>25</v>
       </c>
       <c r="D21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>7</v>
@@ -1952,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="b">
         <v>1</v>
@@ -1961,7 +1961,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -1981,7 +1981,7 @@
         <v>25</v>
       </c>
       <c r="D22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2023,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="b">
         <v>1</v>
@@ -2052,7 +2052,7 @@
         <v>25</v>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2094,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="b">
         <v>1</v>
@@ -2103,7 +2103,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2194,7 +2194,7 @@
         <v>25</v>
       </c>
       <c r="D25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="b">
         <v>1</v>
@@ -2245,7 +2245,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2378,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2407,7 +2407,7 @@
         <v>25</v>
       </c>
       <c r="D28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -2449,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="b">
         <v>1</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
         <v>1</v>
@@ -2549,7 +2549,7 @@
         <v>25</v>
       </c>
       <c r="D30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>7</v>
@@ -2591,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="b">
         <v>1</v>
@@ -2600,7 +2600,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -2620,7 +2620,7 @@
         <v>25</v>
       </c>
       <c r="D31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -2662,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="b">
         <v>1</v>
@@ -2671,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -2691,7 +2691,7 @@
         <v>25</v>
       </c>
       <c r="D32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -2733,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="b">
         <v>1</v>
@@ -2742,7 +2742,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -2762,7 +2762,7 @@
         <v>25</v>
       </c>
       <c r="D33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -2804,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="b">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>25</v>
       </c>
       <c r="D34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -2875,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="b">
         <v>1</v>
@@ -2884,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -2946,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3117,7 +3117,7 @@
         <v>25</v>
       </c>
       <c r="D38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>7</v>
@@ -3159,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="b">
         <v>1</v>
@@ -3168,7 +3168,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V38">
         <v>7</v>
@@ -3259,7 +3259,7 @@
         <v>25</v>
       </c>
       <c r="D40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>7</v>
@@ -3301,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="b">
         <v>1</v>
@@ -3310,7 +3310,7 @@
         <v>7</v>
       </c>
       <c r="U40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3372,10 +3372,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41">
         <v>7</v>
@@ -3401,7 +3401,7 @@
         <v>25</v>
       </c>
       <c r="D42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>7</v>
@@ -3443,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="b">
         <v>1</v>
@@ -3472,7 +3472,7 @@
         <v>25</v>
       </c>
       <c r="D43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>7</v>
@@ -3514,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="b">
         <v>1</v>
@@ -3543,7 +3543,7 @@
         <v>25</v>
       </c>
       <c r="D44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>7</v>
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="b">
         <v>1</v>
@@ -3594,7 +3594,7 @@
         <v>7</v>
       </c>
       <c r="U44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44">
         <v>7</v>
@@ -3614,7 +3614,7 @@
         <v>25</v>
       </c>
       <c r="D45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>7</v>
@@ -3656,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="b">
         <v>1</v>
@@ -3665,7 +3665,7 @@
         <v>7</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45">
         <v>7</v>
@@ -3827,7 +3827,7 @@
         <v>25</v>
       </c>
       <c r="D48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>7</v>
@@ -3869,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="b">
         <v>1</v>
@@ -3898,7 +3898,7 @@
         <v>25</v>
       </c>
       <c r="D49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>7</v>
@@ -3940,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="b">
         <v>1</v>
@@ -3949,7 +3949,7 @@
         <v>7</v>
       </c>
       <c r="U49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49">
         <v>7</v>
@@ -3969,7 +3969,7 @@
         <v>25</v>
       </c>
       <c r="D50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>7</v>
@@ -4011,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="b">
         <v>1</v>
@@ -4020,7 +4020,7 @@
         <v>7</v>
       </c>
       <c r="U50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50">
         <v>7</v>
@@ -4040,7 +4040,7 @@
         <v>25</v>
       </c>
       <c r="D51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>7</v>
@@ -4082,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="b">
         <v>1</v>
@@ -4091,7 +4091,7 @@
         <v>7</v>
       </c>
       <c r="U51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51">
         <v>7</v>
@@ -4111,7 +4111,7 @@
         <v>25</v>
       </c>
       <c r="D52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>7</v>
@@ -4153,7 +4153,7 @@
         <v>1</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="b">
         <v>1</v>
@@ -4182,7 +4182,7 @@
         <v>25</v>
       </c>
       <c r="D53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>7</v>
@@ -4224,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="b">
         <v>1</v>
@@ -4233,7 +4233,7 @@
         <v>7</v>
       </c>
       <c r="U53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V53">
         <v>7</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="b">
         <v>1</v>
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="b">
         <v>1</v>
@@ -4466,7 +4466,7 @@
         <v>25</v>
       </c>
       <c r="D57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>7</v>
@@ -4508,7 +4508,7 @@
         <v>1</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="b">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="b">
         <v>1</v>
@@ -4750,7 +4750,7 @@
         <v>25</v>
       </c>
       <c r="D61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>7</v>
@@ -4792,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="b">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>7</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V61">
         <v>7</v>
@@ -4892,7 +4892,7 @@
         <v>25</v>
       </c>
       <c r="D63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>7</v>
@@ -4934,7 +4934,7 @@
         <v>1</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="b">
         <v>1</v>
@@ -4943,7 +4943,7 @@
         <v>7</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V63">
         <v>7</v>
@@ -5034,7 +5034,7 @@
         <v>25</v>
       </c>
       <c r="D65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65">
         <v>7</v>
@@ -5076,7 +5076,7 @@
         <v>1</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="b">
         <v>1</v>
@@ -5105,7 +5105,7 @@
         <v>25</v>
       </c>
       <c r="D66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66">
         <v>7</v>
@@ -5147,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="R66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="b">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>25</v>
       </c>
       <c r="D67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>7</v>
@@ -5218,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="b">
         <v>1</v>
@@ -5227,7 +5227,7 @@
         <v>7</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V67">
         <v>7</v>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="b">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>25</v>
       </c>
       <c r="D70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>1</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="b">
         <v>1</v>
@@ -5440,7 +5440,7 @@
         <v>7</v>
       </c>
       <c r="U70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V70">
         <v>7</v>
@@ -5460,7 +5460,7 @@
         <v>25</v>
       </c>
       <c r="D71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>7</v>
@@ -5502,7 +5502,7 @@
         <v>1</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="b">
         <v>1</v>
@@ -5511,7 +5511,7 @@
         <v>7</v>
       </c>
       <c r="U71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V71">
         <v>7</v>
@@ -5531,7 +5531,7 @@
         <v>25</v>
       </c>
       <c r="D72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>7</v>
@@ -5573,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="b">
         <v>1</v>
@@ -5582,7 +5582,7 @@
         <v>7</v>
       </c>
       <c r="U72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V72">
         <v>7</v>
@@ -5602,7 +5602,7 @@
         <v>25</v>
       </c>
       <c r="D73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>7</v>
@@ -5644,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="b">
         <v>1</v>
@@ -5653,7 +5653,7 @@
         <v>7</v>
       </c>
       <c r="U73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73">
         <v>7</v>
@@ -5673,7 +5673,7 @@
         <v>25</v>
       </c>
       <c r="D74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>7</v>
@@ -5715,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="b">
         <v>1</v>
@@ -5724,7 +5724,7 @@
         <v>7</v>
       </c>
       <c r="U74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V74">
         <v>7</v>
@@ -5786,10 +5786,10 @@
         <v>0</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75">
         <v>7</v>
@@ -5815,7 +5815,7 @@
         <v>25</v>
       </c>
       <c r="D76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>7</v>
@@ -5857,7 +5857,7 @@
         <v>1</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="b">
         <v>1</v>
@@ -5866,7 +5866,7 @@
         <v>7</v>
       </c>
       <c r="U76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V76">
         <v>7</v>
@@ -5886,7 +5886,7 @@
         <v>25</v>
       </c>
       <c r="D77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>7</v>
@@ -5928,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="b">
         <v>1</v>
@@ -5937,7 +5937,7 @@
         <v>7</v>
       </c>
       <c r="U77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V77">
         <v>7</v>
@@ -5957,7 +5957,7 @@
         <v>25</v>
       </c>
       <c r="D78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>7</v>
@@ -5999,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="b">
         <v>1</v>
@@ -6008,7 +6008,7 @@
         <v>7</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V78">
         <v>7</v>
@@ -6028,7 +6028,7 @@
         <v>25</v>
       </c>
       <c r="D79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>7</v>
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="b">
         <v>1</v>
@@ -6079,7 +6079,7 @@
         <v>7</v>
       </c>
       <c r="U79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V79">
         <v>7</v>
@@ -6170,7 +6170,7 @@
         <v>25</v>
       </c>
       <c r="D81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81">
         <v>7</v>
@@ -6212,7 +6212,7 @@
         <v>1</v>
       </c>
       <c r="R81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="b">
         <v>1</v>
@@ -6283,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="R82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="b">
         <v>1</v>
@@ -6354,10 +6354,10 @@
         <v>0</v>
       </c>
       <c r="R83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83">
         <v>7</v>
@@ -6567,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="b">
         <v>1</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="b">
         <v>1</v>
@@ -6667,7 +6667,7 @@
         <v>25</v>
       </c>
       <c r="D88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>7</v>
@@ -6709,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="b">
         <v>1</v>
@@ -6718,7 +6718,7 @@
         <v>7</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V88">
         <v>7</v>
@@ -6738,7 +6738,7 @@
         <v>25</v>
       </c>
       <c r="D89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>7</v>
@@ -6780,7 +6780,7 @@
         <v>1</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="b">
         <v>1</v>
@@ -6789,7 +6789,7 @@
         <v>7</v>
       </c>
       <c r="U89">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V89">
         <v>7</v>
@@ -6851,10 +6851,10 @@
         <v>0</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90">
         <v>7</v>
@@ -6880,7 +6880,7 @@
         <v>25</v>
       </c>
       <c r="D91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>7</v>
@@ -6922,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="b">
         <v>1</v>
@@ -6931,7 +6931,7 @@
         <v>7</v>
       </c>
       <c r="U91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91">
         <v>7</v>
@@ -6951,7 +6951,7 @@
         <v>25</v>
       </c>
       <c r="D92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>7</v>
@@ -6993,7 +6993,7 @@
         <v>1</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="b">
         <v>1</v>
@@ -7002,7 +7002,7 @@
         <v>7</v>
       </c>
       <c r="U92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V92">
         <v>7</v>
@@ -7093,7 +7093,7 @@
         <v>25</v>
       </c>
       <c r="D94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>7</v>
@@ -7135,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="b">
         <v>1</v>
@@ -7144,7 +7144,7 @@
         <v>7</v>
       </c>
       <c r="U94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V94">
         <v>7</v>
@@ -7306,7 +7306,7 @@
         <v>25</v>
       </c>
       <c r="D97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>7</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="R97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="b">
         <v>1</v>
@@ -7357,7 +7357,7 @@
         <v>7</v>
       </c>
       <c r="U97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V97">
         <v>7</v>
@@ -7419,10 +7419,10 @@
         <v>0</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98">
         <v>7</v>
@@ -7448,7 +7448,7 @@
         <v>25</v>
       </c>
       <c r="D99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>7</v>
@@ -7490,7 +7490,7 @@
         <v>1</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="b">
         <v>1</v>
@@ -7499,7 +7499,7 @@
         <v>7</v>
       </c>
       <c r="U99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V99">
         <v>7</v>
@@ -7519,7 +7519,7 @@
         <v>25</v>
       </c>
       <c r="D100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>7</v>
@@ -7561,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="b">
         <v>1</v>
@@ -7570,7 +7570,7 @@
         <v>7</v>
       </c>
       <c r="U100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V100">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>25</v>
       </c>
       <c r="D101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>7</v>
@@ -7632,7 +7632,7 @@
         <v>1</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="b">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v>25</v>
       </c>
       <c r="D102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>7</v>
@@ -7703,7 +7703,7 @@
         <v>1</v>
       </c>
       <c r="R102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="b">
         <v>1</v>
@@ -7712,7 +7712,7 @@
         <v>7</v>
       </c>
       <c r="U102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V102">
         <v>7</v>
@@ -7732,7 +7732,7 @@
         <v>25</v>
       </c>
       <c r="D103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>7</v>
@@ -7774,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="R103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="b">
         <v>1</v>
@@ -7874,7 +7874,7 @@
         <v>25</v>
       </c>
       <c r="D105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>7</v>
@@ -7916,7 +7916,7 @@
         <v>1</v>
       </c>
       <c r="R105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S105" t="b">
         <v>1</v>
@@ -7945,7 +7945,7 @@
         <v>25</v>
       </c>
       <c r="D106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>7</v>
@@ -7987,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="R106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S106" t="b">
         <v>1</v>
@@ -7996,7 +7996,7 @@
         <v>7</v>
       </c>
       <c r="U106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V106">
         <v>7</v>
@@ -8016,7 +8016,7 @@
         <v>25</v>
       </c>
       <c r="D107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>7</v>
@@ -8058,7 +8058,7 @@
         <v>1</v>
       </c>
       <c r="R107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S107" t="b">
         <v>1</v>
@@ -8067,7 +8067,7 @@
         <v>7</v>
       </c>
       <c r="U107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V107">
         <v>7</v>
@@ -8087,7 +8087,7 @@
         <v>25</v>
       </c>
       <c r="D108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>7</v>
@@ -8129,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="R108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S108" t="b">
         <v>1</v>
@@ -8158,7 +8158,7 @@
         <v>25</v>
       </c>
       <c r="D109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>7</v>
@@ -8200,7 +8200,7 @@
         <v>1</v>
       </c>
       <c r="R109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S109" t="b">
         <v>1</v>
@@ -8209,7 +8209,7 @@
         <v>7</v>
       </c>
       <c r="U109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V109">
         <v>7</v>
@@ -8229,7 +8229,7 @@
         <v>25</v>
       </c>
       <c r="D110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110">
         <v>7</v>
@@ -8271,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="R110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S110" t="b">
         <v>1</v>
@@ -8280,7 +8280,7 @@
         <v>7</v>
       </c>
       <c r="U110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V110">
         <v>7</v>
@@ -8300,7 +8300,7 @@
         <v>25</v>
       </c>
       <c r="D111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>7</v>
@@ -8342,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="R111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="b">
         <v>1</v>
@@ -8351,7 +8351,7 @@
         <v>7</v>
       </c>
       <c r="U111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V111">
         <v>7</v>
@@ -8371,7 +8371,7 @@
         <v>25</v>
       </c>
       <c r="D112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>7</v>
@@ -8413,7 +8413,7 @@
         <v>1</v>
       </c>
       <c r="R112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S112" t="b">
         <v>1</v>
@@ -8422,7 +8422,7 @@
         <v>7</v>
       </c>
       <c r="U112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V112">
         <v>7</v>
@@ -8484,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="R113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113">
         <v>7</v>
@@ -8513,7 +8513,7 @@
         <v>25</v>
       </c>
       <c r="D114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>7</v>
@@ -8555,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="R114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S114" t="b">
         <v>1</v>
@@ -8655,7 +8655,7 @@
         <v>25</v>
       </c>
       <c r="D116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>7</v>
@@ -8697,7 +8697,7 @@
         <v>1</v>
       </c>
       <c r="R116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S116" t="b">
         <v>1</v>
@@ -8726,7 +8726,7 @@
         <v>25</v>
       </c>
       <c r="D117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>7</v>
@@ -8768,7 +8768,7 @@
         <v>1</v>
       </c>
       <c r="R117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S117" t="b">
         <v>1</v>
@@ -9052,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="R121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="b">
         <v>1</v>
@@ -9123,10 +9123,10 @@
         <v>0</v>
       </c>
       <c r="R122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122">
         <v>7</v>
@@ -9152,7 +9152,7 @@
         <v>25</v>
       </c>
       <c r="D123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>7</v>
@@ -9194,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="R123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S123" t="b">
         <v>1</v>
@@ -9203,7 +9203,7 @@
         <v>7</v>
       </c>
       <c r="U123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V123">
         <v>7</v>
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="b">
         <v>1</v>
@@ -9407,10 +9407,10 @@
         <v>0</v>
       </c>
       <c r="R126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126">
         <v>7</v>
@@ -9436,7 +9436,7 @@
         <v>25</v>
       </c>
       <c r="D127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>7</v>
@@ -9478,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="R127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="b">
         <v>1</v>
@@ -9487,7 +9487,7 @@
         <v>7</v>
       </c>
       <c r="U127">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V127">
         <v>7</v>
@@ -9507,7 +9507,7 @@
         <v>25</v>
       </c>
       <c r="D128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>7</v>
@@ -9549,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="R128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="b">
         <v>1</v>
@@ -9558,7 +9558,7 @@
         <v>7</v>
       </c>
       <c r="U128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V128">
         <v>7</v>
@@ -9578,7 +9578,7 @@
         <v>25</v>
       </c>
       <c r="D129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>7</v>
@@ -9620,7 +9620,7 @@
         <v>1</v>
       </c>
       <c r="R129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" t="b">
         <v>1</v>
@@ -9629,7 +9629,7 @@
         <v>7</v>
       </c>
       <c r="U129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V129">
         <v>7</v>
@@ -9649,7 +9649,7 @@
         <v>25</v>
       </c>
       <c r="D130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>7</v>
@@ -9691,7 +9691,7 @@
         <v>1</v>
       </c>
       <c r="R130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S130" t="b">
         <v>1</v>
@@ -9720,7 +9720,7 @@
         <v>25</v>
       </c>
       <c r="D131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>7</v>
@@ -9762,7 +9762,7 @@
         <v>1</v>
       </c>
       <c r="R131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S131" t="b">
         <v>1</v>
@@ -9771,7 +9771,7 @@
         <v>7</v>
       </c>
       <c r="U131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V131">
         <v>7</v>
@@ -9933,7 +9933,7 @@
         <v>25</v>
       </c>
       <c r="D134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>7</v>
@@ -9975,7 +9975,7 @@
         <v>1</v>
       </c>
       <c r="R134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S134" t="b">
         <v>1</v>
@@ -9984,7 +9984,7 @@
         <v>7</v>
       </c>
       <c r="U134">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V134">
         <v>7</v>
@@ -10046,10 +10046,10 @@
         <v>0</v>
       </c>
       <c r="R135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T135">
         <v>7</v>
@@ -10188,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="b">
         <v>1</v>
@@ -10288,7 +10288,7 @@
         <v>25</v>
       </c>
       <c r="D139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>7</v>
@@ -10330,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="R139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S139" t="b">
         <v>1</v>
@@ -10339,7 +10339,7 @@
         <v>7</v>
       </c>
       <c r="U139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V139">
         <v>7</v>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S140" t="b">
         <v>1</v>
@@ -10543,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="R142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S142" t="b">
         <v>1</v>
@@ -10685,10 +10685,10 @@
         <v>0</v>
       </c>
       <c r="R144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T144">
         <v>7</v>
@@ -10785,7 +10785,7 @@
         <v>25</v>
       </c>
       <c r="D146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146">
         <v>7</v>
@@ -10827,7 +10827,7 @@
         <v>1</v>
       </c>
       <c r="R146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S146" t="b">
         <v>1</v>
@@ -10836,7 +10836,7 @@
         <v>7</v>
       </c>
       <c r="U146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V146">
         <v>7</v>
@@ -10927,7 +10927,7 @@
         <v>25</v>
       </c>
       <c r="D148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>7</v>
@@ -10969,7 +10969,7 @@
         <v>1</v>
       </c>
       <c r="R148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S148" t="b">
         <v>1</v>
@@ -10998,7 +10998,7 @@
         <v>25</v>
       </c>
       <c r="D149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>7</v>
@@ -11040,7 +11040,7 @@
         <v>1</v>
       </c>
       <c r="R149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S149" t="b">
         <v>1</v>
@@ -11049,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="U149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V149">
         <v>7</v>
@@ -11182,7 +11182,7 @@
         <v>0</v>
       </c>
       <c r="R151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>
@@ -11211,7 +11211,7 @@
         <v>25</v>
       </c>
       <c r="D152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152">
         <v>7</v>
@@ -11253,7 +11253,7 @@
         <v>1</v>
       </c>
       <c r="R152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S152" t="b">
         <v>1</v>
@@ -11282,7 +11282,7 @@
         <v>25</v>
       </c>
       <c r="D153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153">
         <v>7</v>
@@ -11324,7 +11324,7 @@
         <v>1</v>
       </c>
       <c r="R153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S153" t="b">
         <v>1</v>
@@ -11333,7 +11333,7 @@
         <v>6</v>
       </c>
       <c r="U153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V153">
         <v>6</v>
@@ -11395,10 +11395,10 @@
         <v>0</v>
       </c>
       <c r="R154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154">
         <v>7</v>
@@ -11495,7 +11495,7 @@
         <v>25</v>
       </c>
       <c r="D156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156">
         <v>7</v>
@@ -11537,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="R156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S156" t="b">
         <v>1</v>
@@ -11546,7 +11546,7 @@
         <v>7</v>
       </c>
       <c r="U156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V156">
         <v>7</v>
@@ -11608,7 +11608,7 @@
         <v>0</v>
       </c>
       <c r="R157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S157" t="b">
         <v>1</v>
@@ -11637,7 +11637,7 @@
         <v>25</v>
       </c>
       <c r="D158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>7</v>
@@ -11679,7 +11679,7 @@
         <v>1</v>
       </c>
       <c r="R158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S158" t="b">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>7</v>
       </c>
       <c r="U158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V158">
         <v>7</v>
@@ -11708,7 +11708,7 @@
         <v>25</v>
       </c>
       <c r="D159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159">
         <v>7</v>
@@ -11750,7 +11750,7 @@
         <v>1</v>
       </c>
       <c r="R159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S159" t="b">
         <v>1</v>
@@ -11759,7 +11759,7 @@
         <v>7</v>
       </c>
       <c r="U159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V159">
         <v>7</v>
@@ -11892,7 +11892,7 @@
         <v>0</v>
       </c>
       <c r="R161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S161" t="b">
         <v>1</v>
@@ -11921,7 +11921,7 @@
         <v>25</v>
       </c>
       <c r="D162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162">
         <v>7</v>
@@ -11963,7 +11963,7 @@
         <v>1</v>
       </c>
       <c r="R162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S162" t="b">
         <v>1</v>
@@ -12063,7 +12063,7 @@
         <v>25</v>
       </c>
       <c r="D164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164">
         <v>7</v>
@@ -12105,7 +12105,7 @@
         <v>1</v>
       </c>
       <c r="R164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S164" t="b">
         <v>1</v>
@@ -12114,7 +12114,7 @@
         <v>7</v>
       </c>
       <c r="U164">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V164">
         <v>7</v>
@@ -12134,7 +12134,7 @@
         <v>25</v>
       </c>
       <c r="D165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165">
         <v>7</v>
@@ -12176,7 +12176,7 @@
         <v>1</v>
       </c>
       <c r="R165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S165" t="b">
         <v>1</v>
@@ -12185,7 +12185,7 @@
         <v>7</v>
       </c>
       <c r="U165">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V165">
         <v>7</v>
@@ -12276,7 +12276,7 @@
         <v>25</v>
       </c>
       <c r="D167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167">
         <v>7</v>
@@ -12318,7 +12318,7 @@
         <v>1</v>
       </c>
       <c r="R167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S167" t="b">
         <v>1</v>
@@ -12327,7 +12327,7 @@
         <v>7</v>
       </c>
       <c r="U167">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V167">
         <v>7</v>
@@ -12347,7 +12347,7 @@
         <v>25</v>
       </c>
       <c r="D168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168">
         <v>7</v>
@@ -12389,7 +12389,7 @@
         <v>1</v>
       </c>
       <c r="R168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S168" t="b">
         <v>1</v>
@@ -12398,7 +12398,7 @@
         <v>7</v>
       </c>
       <c r="U168">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V168">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>25</v>
       </c>
       <c r="D169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>7</v>
@@ -12460,7 +12460,7 @@
         <v>1</v>
       </c>
       <c r="R169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S169" t="b">
         <v>1</v>
@@ -12531,7 +12531,7 @@
         <v>0</v>
       </c>
       <c r="R170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S170" t="b">
         <v>1</v>
@@ -12560,7 +12560,7 @@
         <v>25</v>
       </c>
       <c r="D171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>7</v>
@@ -12602,7 +12602,7 @@
         <v>1</v>
       </c>
       <c r="R171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S171" t="b">
         <v>1</v>
@@ -12667,10 +12667,10 @@
         <v>1</v>
       </c>
       <c r="R172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T172">
         <v>7</v>
@@ -12761,7 +12761,7 @@
         <v>25</v>
       </c>
       <c r="D174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174">
         <v>7</v>
@@ -12797,7 +12797,7 @@
         <v>1</v>
       </c>
       <c r="R174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S174" t="b">
         <v>1</v>
@@ -12806,7 +12806,7 @@
         <v>7</v>
       </c>
       <c r="U174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V174">
         <v>7</v>
@@ -12927,10 +12927,10 @@
         <v>0</v>
       </c>
       <c r="R176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176">
         <v>7</v>
@@ -12992,10 +12992,10 @@
         <v>0</v>
       </c>
       <c r="R177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T177">
         <v>7</v>
@@ -13021,7 +13021,7 @@
         <v>25</v>
       </c>
       <c r="D178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>7</v>
@@ -13057,7 +13057,7 @@
         <v>1</v>
       </c>
       <c r="R178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S178" t="b">
         <v>1</v>
@@ -13066,7 +13066,7 @@
         <v>7</v>
       </c>
       <c r="U178">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V178">
         <v>7</v>
@@ -13086,7 +13086,7 @@
         <v>25</v>
       </c>
       <c r="D179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179">
         <v>7</v>
@@ -13122,7 +13122,7 @@
         <v>1</v>
       </c>
       <c r="R179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S179" t="b">
         <v>1</v>
@@ -13131,7 +13131,7 @@
         <v>7</v>
       </c>
       <c r="U179">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V179">
         <v>7</v>
@@ -13216,7 +13216,7 @@
         <v>25</v>
       </c>
       <c r="D181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181">
         <v>7</v>
@@ -13252,7 +13252,7 @@
         <v>1</v>
       </c>
       <c r="R181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S181" t="b">
         <v>1</v>
@@ -13261,7 +13261,7 @@
         <v>7</v>
       </c>
       <c r="U181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V181">
         <v>7</v>
@@ -13281,7 +13281,7 @@
         <v>25</v>
       </c>
       <c r="D182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182">
         <v>7</v>
@@ -13317,7 +13317,7 @@
         <v>1</v>
       </c>
       <c r="R182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S182" t="b">
         <v>1</v>
@@ -13326,7 +13326,7 @@
         <v>7</v>
       </c>
       <c r="U182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V182">
         <v>7</v>
@@ -13411,7 +13411,7 @@
         <v>25</v>
       </c>
       <c r="D184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184">
         <v>7</v>
@@ -13447,7 +13447,7 @@
         <v>1</v>
       </c>
       <c r="R184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S184" t="b">
         <v>1</v>
@@ -13456,7 +13456,7 @@
         <v>7</v>
       </c>
       <c r="U184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V184">
         <v>7</v>
@@ -13476,7 +13476,7 @@
         <v>25</v>
       </c>
       <c r="D185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>7</v>
@@ -13512,7 +13512,7 @@
         <v>1</v>
       </c>
       <c r="R185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S185" t="b">
         <v>1</v>
@@ -13541,7 +13541,7 @@
         <v>25</v>
       </c>
       <c r="D186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186">
         <v>7</v>
@@ -13577,7 +13577,7 @@
         <v>1</v>
       </c>
       <c r="R186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S186" t="b">
         <v>1</v>
@@ -13671,7 +13671,7 @@
         <v>25</v>
       </c>
       <c r="D188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>7</v>
@@ -13707,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="R188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S188" t="b">
         <v>1</v>
@@ -13716,7 +13716,7 @@
         <v>7</v>
       </c>
       <c r="U188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V188">
         <v>7</v>
@@ -13772,7 +13772,7 @@
         <v>0</v>
       </c>
       <c r="R189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S189" t="b">
         <v>1</v>
@@ -13837,10 +13837,10 @@
         <v>1</v>
       </c>
       <c r="R190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T190">
         <v>7</v>
@@ -13866,7 +13866,7 @@
         <v>25</v>
       </c>
       <c r="D191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E191">
         <v>7</v>
@@ -13902,7 +13902,7 @@
         <v>1</v>
       </c>
       <c r="R191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S191" t="b">
         <v>1</v>
@@ -13931,7 +13931,7 @@
         <v>25</v>
       </c>
       <c r="D192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>7</v>
@@ -13967,7 +13967,7 @@
         <v>1</v>
       </c>
       <c r="R192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S192" t="b">
         <v>1</v>
@@ -13976,7 +13976,7 @@
         <v>7</v>
       </c>
       <c r="U192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V192">
         <v>7</v>
@@ -13996,7 +13996,7 @@
         <v>25</v>
       </c>
       <c r="D193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193">
         <v>7</v>
@@ -14032,7 +14032,7 @@
         <v>1</v>
       </c>
       <c r="R193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S193" t="b">
         <v>1</v>
@@ -14041,7 +14041,7 @@
         <v>7</v>
       </c>
       <c r="U193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V193">
         <v>7</v>
@@ -14097,10 +14097,10 @@
         <v>0</v>
       </c>
       <c r="R194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T194">
         <v>7</v>
@@ -14126,7 +14126,7 @@
         <v>25</v>
       </c>
       <c r="D195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195">
         <v>7</v>
@@ -14162,7 +14162,7 @@
         <v>1</v>
       </c>
       <c r="R195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S195" t="b">
         <v>1</v>
@@ -14292,10 +14292,10 @@
         <v>1</v>
       </c>
       <c r="R197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T197">
         <v>7</v>
@@ -14321,7 +14321,7 @@
         <v>25</v>
       </c>
       <c r="D198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E198">
         <v>7</v>
@@ -14357,7 +14357,7 @@
         <v>1</v>
       </c>
       <c r="R198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S198" t="b">
         <v>1</v>
@@ -14386,7 +14386,7 @@
         <v>25</v>
       </c>
       <c r="D199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E199">
         <v>7</v>
@@ -14422,7 +14422,7 @@
         <v>1</v>
       </c>
       <c r="R199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S199" t="b">
         <v>1</v>
@@ -14431,7 +14431,7 @@
         <v>7</v>
       </c>
       <c r="U199">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V199">
         <v>7</v>
@@ -14451,7 +14451,7 @@
         <v>25</v>
       </c>
       <c r="D200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E200">
         <v>7</v>
@@ -14487,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="R200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S200" t="b">
         <v>1</v>
@@ -14496,7 +14496,7 @@
         <v>7</v>
       </c>
       <c r="U200">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V200">
         <v>7</v>
@@ -14516,7 +14516,7 @@
         <v>25</v>
       </c>
       <c r="D201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201">
         <v>7</v>
@@ -14552,7 +14552,7 @@
         <v>1</v>
       </c>
       <c r="R201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S201" t="b">
         <v>1</v>
@@ -14581,7 +14581,7 @@
         <v>25</v>
       </c>
       <c r="D202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202">
         <v>7</v>
@@ -14617,7 +14617,7 @@
         <v>1</v>
       </c>
       <c r="R202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S202" t="b">
         <v>1</v>
@@ -14626,7 +14626,7 @@
         <v>7</v>
       </c>
       <c r="U202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V202">
         <v>7</v>
@@ -14646,7 +14646,7 @@
         <v>25</v>
       </c>
       <c r="D203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203">
         <v>7</v>
@@ -14682,7 +14682,7 @@
         <v>1</v>
       </c>
       <c r="R203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S203" t="b">
         <v>1</v>
@@ -14691,7 +14691,7 @@
         <v>7</v>
       </c>
       <c r="U203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V203">
         <v>7</v>
@@ -14711,7 +14711,7 @@
         <v>25</v>
       </c>
       <c r="D204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204">
         <v>7</v>
@@ -14747,7 +14747,7 @@
         <v>1</v>
       </c>
       <c r="R204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S204" t="b">
         <v>1</v>
@@ -14756,7 +14756,7 @@
         <v>7</v>
       </c>
       <c r="U204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V204">
         <v>7</v>
@@ -14812,10 +14812,10 @@
         <v>0</v>
       </c>
       <c r="R205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T205">
         <v>7</v>
@@ -14971,7 +14971,7 @@
         <v>25</v>
       </c>
       <c r="D208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208">
         <v>7</v>
@@ -15007,7 +15007,7 @@
         <v>1</v>
       </c>
       <c r="R208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S208" t="b">
         <v>1</v>
@@ -15101,7 +15101,7 @@
         <v>25</v>
       </c>
       <c r="D210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210">
         <v>7</v>
@@ -15137,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="R210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S210" t="b">
         <v>1</v>
@@ -15202,10 +15202,10 @@
         <v>1</v>
       </c>
       <c r="R211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T211">
         <v>7</v>
@@ -15231,7 +15231,7 @@
         <v>25</v>
       </c>
       <c r="D212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E212">
         <v>7</v>
@@ -15267,7 +15267,7 @@
         <v>1</v>
       </c>
       <c r="R212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S212" t="b">
         <v>1</v>
@@ -15276,7 +15276,7 @@
         <v>7</v>
       </c>
       <c r="U212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V212">
         <v>7</v>
@@ -15296,7 +15296,7 @@
         <v>25</v>
       </c>
       <c r="D213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>7</v>
@@ -15332,7 +15332,7 @@
         <v>1</v>
       </c>
       <c r="R213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S213" t="b">
         <v>1</v>
@@ -15361,7 +15361,7 @@
         <v>25</v>
       </c>
       <c r="D214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E214">
         <v>7</v>
@@ -15397,7 +15397,7 @@
         <v>1</v>
       </c>
       <c r="R214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S214" t="b">
         <v>1</v>
@@ -15426,7 +15426,7 @@
         <v>25</v>
       </c>
       <c r="D215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E215">
         <v>7</v>
@@ -15462,7 +15462,7 @@
         <v>1</v>
       </c>
       <c r="R215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S215" t="b">
         <v>1</v>
@@ -15471,7 +15471,7 @@
         <v>7</v>
       </c>
       <c r="U215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V215">
         <v>7</v>
@@ -15621,7 +15621,7 @@
         <v>25</v>
       </c>
       <c r="D218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218">
         <v>7</v>
@@ -15657,7 +15657,7 @@
         <v>1</v>
       </c>
       <c r="R218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S218" t="b">
         <v>1</v>
@@ -15666,7 +15666,7 @@
         <v>7</v>
       </c>
       <c r="U218">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V218">
         <v>7</v>
@@ -15686,7 +15686,7 @@
         <v>25</v>
       </c>
       <c r="D219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219">
         <v>7</v>
@@ -15722,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="R219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S219" t="b">
         <v>1</v>
@@ -15751,7 +15751,7 @@
         <v>25</v>
       </c>
       <c r="D220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220">
         <v>7</v>
@@ -15787,7 +15787,7 @@
         <v>1</v>
       </c>
       <c r="R220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S220" t="b">
         <v>1</v>
@@ -15816,7 +15816,7 @@
         <v>25</v>
       </c>
       <c r="D221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>7</v>
@@ -15852,7 +15852,7 @@
         <v>1</v>
       </c>
       <c r="R221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S221" t="b">
         <v>1</v>
@@ -15861,7 +15861,7 @@
         <v>7</v>
       </c>
       <c r="U221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V221">
         <v>7</v>
@@ -15881,7 +15881,7 @@
         <v>25</v>
       </c>
       <c r="D222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E222">
         <v>7</v>
@@ -15917,7 +15917,7 @@
         <v>1</v>
       </c>
       <c r="R222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S222" t="b">
         <v>1</v>
@@ -15946,7 +15946,7 @@
         <v>25</v>
       </c>
       <c r="D223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>7</v>
@@ -15982,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="R223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S223" t="b">
         <v>1</v>
@@ -15991,7 +15991,7 @@
         <v>7</v>
       </c>
       <c r="U223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V223">
         <v>7</v>
@@ -16047,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="R224" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S224" t="b">
         <v>1</v>
@@ -16076,7 +16076,7 @@
         <v>25</v>
       </c>
       <c r="D225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E225">
         <v>7</v>
@@ -16112,7 +16112,7 @@
         <v>1</v>
       </c>
       <c r="R225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S225" t="b">
         <v>1</v>
@@ -16121,7 +16121,7 @@
         <v>7</v>
       </c>
       <c r="U225">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V225">
         <v>7</v>
@@ -16206,7 +16206,7 @@
         <v>25</v>
       </c>
       <c r="D227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>7</v>
@@ -16242,7 +16242,7 @@
         <v>1</v>
       </c>
       <c r="R227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S227" t="b">
         <v>1</v>
@@ -16401,7 +16401,7 @@
         <v>25</v>
       </c>
       <c r="D230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E230">
         <v>7</v>
@@ -16437,7 +16437,7 @@
         <v>1</v>
       </c>
       <c r="R230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S230" t="b">
         <v>1</v>
@@ -16466,7 +16466,7 @@
         <v>25</v>
       </c>
       <c r="D231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>7</v>
@@ -16502,7 +16502,7 @@
         <v>1</v>
       </c>
       <c r="R231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S231" t="b">
         <v>1</v>
@@ -16511,7 +16511,7 @@
         <v>7</v>
       </c>
       <c r="U231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V231">
         <v>7</v>
@@ -16596,7 +16596,7 @@
         <v>25</v>
       </c>
       <c r="D233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>7</v>
@@ -16632,7 +16632,7 @@
         <v>1</v>
       </c>
       <c r="R233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S233" t="b">
         <v>1</v>
@@ -16641,7 +16641,7 @@
         <v>7</v>
       </c>
       <c r="U233">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V233">
         <v>7</v>
@@ -16726,7 +16726,7 @@
         <v>25</v>
       </c>
       <c r="D235" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235">
         <v>7</v>
@@ -16762,7 +16762,7 @@
         <v>1</v>
       </c>
       <c r="R235" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S235" t="b">
         <v>1</v>
@@ -16771,7 +16771,7 @@
         <v>7</v>
       </c>
       <c r="U235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V235">
         <v>7</v>
@@ -16791,7 +16791,7 @@
         <v>25</v>
       </c>
       <c r="D236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236">
         <v>7</v>
@@ -16827,7 +16827,7 @@
         <v>1</v>
       </c>
       <c r="R236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S236" t="b">
         <v>1</v>
@@ -16836,7 +16836,7 @@
         <v>7</v>
       </c>
       <c r="U236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V236">
         <v>7</v>
@@ -16856,7 +16856,7 @@
         <v>25</v>
       </c>
       <c r="D237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>7</v>
@@ -16892,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="R237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S237" t="b">
         <v>1</v>
@@ -16901,7 +16901,7 @@
         <v>7</v>
       </c>
       <c r="U237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V237">
         <v>7</v>
@@ -16921,7 +16921,7 @@
         <v>25</v>
       </c>
       <c r="D238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238">
         <v>7</v>
@@ -16957,7 +16957,7 @@
         <v>1</v>
       </c>
       <c r="R238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S238" t="b">
         <v>1</v>
@@ -16966,7 +16966,7 @@
         <v>7</v>
       </c>
       <c r="U238">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V238">
         <v>7</v>
@@ -17051,7 +17051,7 @@
         <v>25</v>
       </c>
       <c r="D240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>7</v>
@@ -17087,7 +17087,7 @@
         <v>1</v>
       </c>
       <c r="R240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S240" t="b">
         <v>1</v>
@@ -17096,7 +17096,7 @@
         <v>7</v>
       </c>
       <c r="U240">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V240">
         <v>7</v>
@@ -17116,7 +17116,7 @@
         <v>25</v>
       </c>
       <c r="D241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>7</v>
@@ -17152,7 +17152,7 @@
         <v>1</v>
       </c>
       <c r="R241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S241" t="b">
         <v>1</v>
@@ -17161,7 +17161,7 @@
         <v>7</v>
       </c>
       <c r="U241">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V241">
         <v>7</v>
@@ -17181,7 +17181,7 @@
         <v>25</v>
       </c>
       <c r="D242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E242">
         <v>7</v>
@@ -17217,7 +17217,7 @@
         <v>1</v>
       </c>
       <c r="R242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S242" t="b">
         <v>1</v>
@@ -17226,7 +17226,7 @@
         <v>7</v>
       </c>
       <c r="U242">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V242">
         <v>7</v>
@@ -17246,7 +17246,7 @@
         <v>25</v>
       </c>
       <c r="D243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E243">
         <v>7</v>
@@ -17282,7 +17282,7 @@
         <v>1</v>
       </c>
       <c r="R243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S243" t="b">
         <v>1</v>
@@ -17291,7 +17291,7 @@
         <v>7</v>
       </c>
       <c r="U243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V243">
         <v>7</v>
@@ -17311,7 +17311,7 @@
         <v>25</v>
       </c>
       <c r="D244" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244">
         <v>7</v>
@@ -17347,7 +17347,7 @@
         <v>1</v>
       </c>
       <c r="R244" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S244" t="b">
         <v>1</v>
@@ -17356,7 +17356,7 @@
         <v>7</v>
       </c>
       <c r="U244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V244">
         <v>7</v>
@@ -17412,10 +17412,10 @@
         <v>0</v>
       </c>
       <c r="R245" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T245">
         <v>7</v>
@@ -17441,7 +17441,7 @@
         <v>25</v>
       </c>
       <c r="D246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246">
         <v>7</v>
@@ -17477,7 +17477,7 @@
         <v>1</v>
       </c>
       <c r="R246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S246" t="b">
         <v>1</v>
@@ -17486,7 +17486,7 @@
         <v>7</v>
       </c>
       <c r="U246">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V246">
         <v>7</v>
@@ -17506,7 +17506,7 @@
         <v>25</v>
       </c>
       <c r="D247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E247">
         <v>7</v>
@@ -17542,7 +17542,7 @@
         <v>1</v>
       </c>
       <c r="R247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S247" t="b">
         <v>1</v>
@@ -17551,7 +17551,7 @@
         <v>7</v>
       </c>
       <c r="U247">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V247">
         <v>7</v>
@@ -17571,7 +17571,7 @@
         <v>25</v>
       </c>
       <c r="D248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248">
         <v>7</v>
@@ -17607,7 +17607,7 @@
         <v>1</v>
       </c>
       <c r="R248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S248" t="b">
         <v>1</v>
@@ -17636,7 +17636,7 @@
         <v>25</v>
       </c>
       <c r="D249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>7</v>
@@ -17672,7 +17672,7 @@
         <v>1</v>
       </c>
       <c r="R249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S249" t="b">
         <v>1</v>
@@ -17681,7 +17681,7 @@
         <v>7</v>
       </c>
       <c r="U249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V249">
         <v>7</v>
@@ -17766,7 +17766,7 @@
         <v>25</v>
       </c>
       <c r="D251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E251">
         <v>7</v>
@@ -17802,7 +17802,7 @@
         <v>1</v>
       </c>
       <c r="R251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S251" t="b">
         <v>1</v>
@@ -17811,7 +17811,7 @@
         <v>7</v>
       </c>
       <c r="U251">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V251">
         <v>7</v>
@@ -17831,7 +17831,7 @@
         <v>25</v>
       </c>
       <c r="D252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252">
         <v>7</v>
@@ -17867,7 +17867,7 @@
         <v>1</v>
       </c>
       <c r="R252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S252" t="b">
         <v>1</v>
@@ -17876,7 +17876,7 @@
         <v>7</v>
       </c>
       <c r="U252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V252">
         <v>7</v>
@@ -17932,10 +17932,10 @@
         <v>0</v>
       </c>
       <c r="R253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T253">
         <v>7</v>
@@ -18091,7 +18091,7 @@
         <v>25</v>
       </c>
       <c r="D256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E256">
         <v>7</v>
@@ -18127,7 +18127,7 @@
         <v>1</v>
       </c>
       <c r="R256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S256" t="b">
         <v>1</v>
@@ -18136,7 +18136,7 @@
         <v>7</v>
       </c>
       <c r="U256">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V256">
         <v>7</v>
@@ -18192,7 +18192,7 @@
         <v>0</v>
       </c>
       <c r="R257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S257" t="b">
         <v>1</v>
@@ -18221,7 +18221,7 @@
         <v>25</v>
       </c>
       <c r="D258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E258">
         <v>7</v>
@@ -18257,7 +18257,7 @@
         <v>1</v>
       </c>
       <c r="R258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S258" t="b">
         <v>1</v>
@@ -18266,7 +18266,7 @@
         <v>7</v>
       </c>
       <c r="U258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V258">
         <v>7</v>
@@ -18286,7 +18286,7 @@
         <v>25</v>
       </c>
       <c r="D259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259">
         <v>7</v>
@@ -18322,7 +18322,7 @@
         <v>1</v>
       </c>
       <c r="R259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S259" t="b">
         <v>1</v>
@@ -18387,10 +18387,10 @@
         <v>0</v>
       </c>
       <c r="R260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T260">
         <v>7</v>
@@ -18416,7 +18416,7 @@
         <v>25</v>
       </c>
       <c r="D261" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261">
         <v>7</v>
@@ -18452,7 +18452,7 @@
         <v>1</v>
       </c>
       <c r="R261" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S261" t="b">
         <v>1</v>
@@ -18461,7 +18461,7 @@
         <v>7</v>
       </c>
       <c r="U261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V261">
         <v>7</v>
@@ -18481,7 +18481,7 @@
         <v>25</v>
       </c>
       <c r="D262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E262">
         <v>7</v>
@@ -18517,7 +18517,7 @@
         <v>1</v>
       </c>
       <c r="R262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S262" t="b">
         <v>1</v>
@@ -18611,7 +18611,7 @@
         <v>25</v>
       </c>
       <c r="D264" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E264">
         <v>7</v>
@@ -18647,7 +18647,7 @@
         <v>1</v>
       </c>
       <c r="R264" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S264" t="b">
         <v>1</v>
@@ -18806,7 +18806,7 @@
         <v>25</v>
       </c>
       <c r="D267" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E267">
         <v>7</v>
@@ -18842,7 +18842,7 @@
         <v>1</v>
       </c>
       <c r="R267" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S267" t="b">
         <v>1</v>
@@ -18851,7 +18851,7 @@
         <v>7</v>
       </c>
       <c r="U267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V267">
         <v>7</v>
@@ -18907,10 +18907,10 @@
         <v>0</v>
       </c>
       <c r="R268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T268">
         <v>7</v>
@@ -18936,7 +18936,7 @@
         <v>25</v>
       </c>
       <c r="D269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E269">
         <v>7</v>
@@ -18972,7 +18972,7 @@
         <v>1</v>
       </c>
       <c r="R269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S269" t="b">
         <v>1</v>
@@ -18981,7 +18981,7 @@
         <v>7</v>
       </c>
       <c r="U269">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V269">
         <v>7</v>
@@ -19001,7 +19001,7 @@
         <v>25</v>
       </c>
       <c r="D270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270">
         <v>7</v>
@@ -19037,7 +19037,7 @@
         <v>1</v>
       </c>
       <c r="R270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S270" t="b">
         <v>1</v>
@@ -19066,7 +19066,7 @@
         <v>25</v>
       </c>
       <c r="D271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>7</v>
@@ -19102,7 +19102,7 @@
         <v>1</v>
       </c>
       <c r="R271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S271" t="b">
         <v>1</v>
@@ -19111,7 +19111,7 @@
         <v>7</v>
       </c>
       <c r="U271">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V271">
         <v>7</v>
@@ -19131,7 +19131,7 @@
         <v>25</v>
       </c>
       <c r="D272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E272">
         <v>7</v>
@@ -19167,7 +19167,7 @@
         <v>1</v>
       </c>
       <c r="R272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S272" t="b">
         <v>1</v>
@@ -19176,7 +19176,7 @@
         <v>7</v>
       </c>
       <c r="U272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V272">
         <v>7</v>
@@ -19196,7 +19196,7 @@
         <v>25</v>
       </c>
       <c r="D273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>7</v>
@@ -19232,7 +19232,7 @@
         <v>1</v>
       </c>
       <c r="R273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S273" t="b">
         <v>1</v>
@@ -19241,7 +19241,7 @@
         <v>7</v>
       </c>
       <c r="U273">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V273">
         <v>7</v>
@@ -19326,7 +19326,7 @@
         <v>25</v>
       </c>
       <c r="D275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>7</v>
@@ -19362,7 +19362,7 @@
         <v>1</v>
       </c>
       <c r="R275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S275" t="b">
         <v>1</v>
@@ -19371,7 +19371,7 @@
         <v>7</v>
       </c>
       <c r="U275">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V275">
         <v>7</v>
@@ -19391,7 +19391,7 @@
         <v>25</v>
       </c>
       <c r="D276" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E276">
         <v>7</v>
@@ -19427,7 +19427,7 @@
         <v>1</v>
       </c>
       <c r="R276" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S276" t="b">
         <v>1</v>
@@ -19456,7 +19456,7 @@
         <v>25</v>
       </c>
       <c r="D277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>7</v>
@@ -19492,7 +19492,7 @@
         <v>1</v>
       </c>
       <c r="R277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S277" t="b">
         <v>1</v>
@@ -19521,7 +19521,7 @@
         <v>25</v>
       </c>
       <c r="D278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E278">
         <v>7</v>
@@ -19557,7 +19557,7 @@
         <v>1</v>
       </c>
       <c r="R278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S278" t="b">
         <v>1</v>
@@ -19586,7 +19586,7 @@
         <v>25</v>
       </c>
       <c r="D279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>7</v>
@@ -19622,7 +19622,7 @@
         <v>1</v>
       </c>
       <c r="R279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S279" t="b">
         <v>1</v>
@@ -19651,7 +19651,7 @@
         <v>25</v>
       </c>
       <c r="D280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E280">
         <v>7</v>
@@ -19687,7 +19687,7 @@
         <v>1</v>
       </c>
       <c r="R280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S280" t="b">
         <v>1</v>
@@ -19696,7 +19696,7 @@
         <v>7</v>
       </c>
       <c r="U280">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V280">
         <v>7</v>
@@ -19716,7 +19716,7 @@
         <v>25</v>
       </c>
       <c r="D281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E281">
         <v>7</v>
@@ -19752,7 +19752,7 @@
         <v>1</v>
       </c>
       <c r="R281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S281" t="b">
         <v>1</v>
@@ -19761,7 +19761,7 @@
         <v>7</v>
       </c>
       <c r="U281">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V281">
         <v>7</v>
@@ -19781,7 +19781,7 @@
         <v>25</v>
       </c>
       <c r="D282" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E282">
         <v>7</v>
@@ -19817,7 +19817,7 @@
         <v>1</v>
       </c>
       <c r="R282" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S282" t="b">
         <v>1</v>
@@ -19826,7 +19826,7 @@
         <v>7</v>
       </c>
       <c r="U282">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V282">
         <v>7</v>
@@ -19882,10 +19882,10 @@
         <v>0</v>
       </c>
       <c r="R283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T283">
         <v>7</v>
@@ -19911,7 +19911,7 @@
         <v>25</v>
       </c>
       <c r="D284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E284">
         <v>7</v>
@@ -19947,7 +19947,7 @@
         <v>1</v>
       </c>
       <c r="R284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S284" t="b">
         <v>1</v>
@@ -20041,7 +20041,7 @@
         <v>25</v>
       </c>
       <c r="D286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E286">
         <v>7</v>
@@ -20077,7 +20077,7 @@
         <v>1</v>
       </c>
       <c r="R286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S286" t="b">
         <v>1</v>
@@ -20086,7 +20086,7 @@
         <v>7</v>
       </c>
       <c r="U286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V286">
         <v>7</v>
@@ -20106,7 +20106,7 @@
         <v>25</v>
       </c>
       <c r="D287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287">
         <v>7</v>
@@ -20142,7 +20142,7 @@
         <v>1</v>
       </c>
       <c r="R287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S287" t="b">
         <v>1</v>
@@ -20151,7 +20151,7 @@
         <v>7</v>
       </c>
       <c r="U287">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V287">
         <v>7</v>
@@ -20402,7 +20402,7 @@
         <v>0</v>
       </c>
       <c r="R291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S291" t="b">
         <v>1</v>
@@ -20467,10 +20467,10 @@
         <v>0</v>
       </c>
       <c r="R292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T292">
         <v>7</v>
@@ -20496,7 +20496,7 @@
         <v>25</v>
       </c>
       <c r="D293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E293">
         <v>7</v>
@@ -20532,7 +20532,7 @@
         <v>1</v>
       </c>
       <c r="R293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S293" t="b">
         <v>1</v>
@@ -20541,7 +20541,7 @@
         <v>7</v>
       </c>
       <c r="U293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V293">
         <v>7</v>
@@ -20597,7 +20597,7 @@
         <v>0</v>
       </c>
       <c r="R294" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S294" t="b">
         <v>1</v>
@@ -20727,10 +20727,10 @@
         <v>0</v>
       </c>
       <c r="R296" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T296">
         <v>7</v>
@@ -20756,7 +20756,7 @@
         <v>25</v>
       </c>
       <c r="D297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E297">
         <v>7</v>
@@ -20792,7 +20792,7 @@
         <v>1</v>
       </c>
       <c r="R297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S297" t="b">
         <v>1</v>
@@ -20801,7 +20801,7 @@
         <v>7</v>
       </c>
       <c r="U297">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V297">
         <v>7</v>
@@ -20821,7 +20821,7 @@
         <v>25</v>
       </c>
       <c r="D298" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E298">
         <v>7</v>
@@ -20857,7 +20857,7 @@
         <v>1</v>
       </c>
       <c r="R298" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S298" t="b">
         <v>1</v>
@@ -20866,7 +20866,7 @@
         <v>7</v>
       </c>
       <c r="U298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V298">
         <v>7</v>
@@ -20886,7 +20886,7 @@
         <v>25</v>
       </c>
       <c r="D299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E299">
         <v>7</v>
@@ -20922,7 +20922,7 @@
         <v>1</v>
       </c>
       <c r="R299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S299" t="b">
         <v>1</v>
@@ -20951,7 +20951,7 @@
         <v>25</v>
       </c>
       <c r="D300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E300">
         <v>7</v>
@@ -20987,7 +20987,7 @@
         <v>1</v>
       </c>
       <c r="R300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S300" t="b">
         <v>1</v>
@@ -21016,7 +21016,7 @@
         <v>25</v>
       </c>
       <c r="D301" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301">
         <v>7</v>
@@ -21052,7 +21052,7 @@
         <v>1</v>
       </c>
       <c r="R301" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S301" t="b">
         <v>1</v>
@@ -21061,7 +21061,7 @@
         <v>7</v>
       </c>
       <c r="U301">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V301">
         <v>7</v>
@@ -21211,7 +21211,7 @@
         <v>25</v>
       </c>
       <c r="D304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E304">
         <v>7</v>
@@ -21247,7 +21247,7 @@
         <v>1</v>
       </c>
       <c r="R304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S304" t="b">
         <v>1</v>
@@ -21256,7 +21256,7 @@
         <v>7</v>
       </c>
       <c r="U304">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V304">
         <v>7</v>
@@ -21312,10 +21312,10 @@
         <v>1</v>
       </c>
       <c r="R305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T305">
         <v>7</v>
@@ -21406,7 +21406,7 @@
         <v>25</v>
       </c>
       <c r="D307" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307">
         <v>7</v>
@@ -21442,7 +21442,7 @@
         <v>1</v>
       </c>
       <c r="R307" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S307" t="b">
         <v>1</v>
@@ -21451,7 +21451,7 @@
         <v>7</v>
       </c>
       <c r="U307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V307">
         <v>7</v>
@@ -21536,7 +21536,7 @@
         <v>25</v>
       </c>
       <c r="D309" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E309">
         <v>7</v>
@@ -21572,7 +21572,7 @@
         <v>1</v>
       </c>
       <c r="R309" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S309" t="b">
         <v>1</v>
@@ -21581,7 +21581,7 @@
         <v>7</v>
       </c>
       <c r="U309">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V309">
         <v>7</v>
@@ -21601,7 +21601,7 @@
         <v>25</v>
       </c>
       <c r="D310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E310">
         <v>7</v>
@@ -21637,7 +21637,7 @@
         <v>1</v>
       </c>
       <c r="R310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S310" t="b">
         <v>1</v>
@@ -21767,7 +21767,7 @@
         <v>0</v>
       </c>
       <c r="R312" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S312" t="b">
         <v>1</v>
@@ -21897,10 +21897,10 @@
         <v>0</v>
       </c>
       <c r="R314" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T314">
         <v>7</v>
@@ -21991,7 +21991,7 @@
         <v>25</v>
       </c>
       <c r="D316" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E316">
         <v>7</v>
@@ -22027,7 +22027,7 @@
         <v>1</v>
       </c>
       <c r="R316" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S316" t="b">
         <v>1</v>
@@ -22036,7 +22036,7 @@
         <v>7</v>
       </c>
       <c r="U316">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V316">
         <v>7</v>
@@ -22121,7 +22121,7 @@
         <v>25</v>
       </c>
       <c r="D318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E318">
         <v>7</v>
@@ -22157,7 +22157,7 @@
         <v>1</v>
       </c>
       <c r="R318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S318" t="b">
         <v>1</v>
@@ -22166,7 +22166,7 @@
         <v>7</v>
       </c>
       <c r="U318">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V318">
         <v>7</v>
@@ -22186,7 +22186,7 @@
         <v>25</v>
       </c>
       <c r="D319" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E319">
         <v>7</v>
@@ -22222,7 +22222,7 @@
         <v>1</v>
       </c>
       <c r="R319" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S319" t="b">
         <v>1</v>
@@ -22231,7 +22231,7 @@
         <v>7</v>
       </c>
       <c r="U319">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V319">
         <v>7</v>
@@ -22316,7 +22316,7 @@
         <v>25</v>
       </c>
       <c r="D321" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E321">
         <v>7</v>
@@ -22352,7 +22352,7 @@
         <v>1</v>
       </c>
       <c r="R321" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S321" t="b">
         <v>1</v>
@@ -22361,7 +22361,7 @@
         <v>7</v>
       </c>
       <c r="U321">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V321">
         <v>7</v>
@@ -22381,7 +22381,7 @@
         <v>25</v>
       </c>
       <c r="D322" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E322">
         <v>7</v>
@@ -22417,7 +22417,7 @@
         <v>1</v>
       </c>
       <c r="R322" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S322" t="b">
         <v>1</v>
@@ -22426,7 +22426,7 @@
         <v>7</v>
       </c>
       <c r="U322">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V322">
         <v>7</v>
@@ -22446,7 +22446,7 @@
         <v>25</v>
       </c>
       <c r="D323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E323">
         <v>7</v>
@@ -22482,7 +22482,7 @@
         <v>1</v>
       </c>
       <c r="R323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S323" t="b">
         <v>1</v>
@@ -22547,10 +22547,10 @@
         <v>0</v>
       </c>
       <c r="R324" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S324" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T324">
         <v>7</v>
@@ -22641,7 +22641,7 @@
         <v>25</v>
       </c>
       <c r="D326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E326">
         <v>7</v>
@@ -22677,7 +22677,7 @@
         <v>1</v>
       </c>
       <c r="R326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S326" t="b">
         <v>1</v>
@@ -22706,7 +22706,7 @@
         <v>25</v>
       </c>
       <c r="D327" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E327">
         <v>7</v>
@@ -22742,7 +22742,7 @@
         <v>1</v>
       </c>
       <c r="R327" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S327" t="b">
         <v>1</v>
@@ -22771,7 +22771,7 @@
         <v>25</v>
       </c>
       <c r="D328" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E328">
         <v>7</v>
@@ -22807,7 +22807,7 @@
         <v>1</v>
       </c>
       <c r="R328" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S328" t="b">
         <v>1</v>
@@ -22836,7 +22836,7 @@
         <v>25</v>
       </c>
       <c r="D329" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E329">
         <v>7</v>
@@ -22872,7 +22872,7 @@
         <v>1</v>
       </c>
       <c r="R329" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S329" t="b">
         <v>1</v>
@@ -22881,7 +22881,7 @@
         <v>7</v>
       </c>
       <c r="U329">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V329">
         <v>7</v>
@@ -22966,7 +22966,7 @@
         <v>25</v>
       </c>
       <c r="D331" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E331">
         <v>7</v>
@@ -23002,7 +23002,7 @@
         <v>1</v>
       </c>
       <c r="R331" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S331" t="b">
         <v>1</v>
@@ -23011,7 +23011,7 @@
         <v>7</v>
       </c>
       <c r="U331">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V331">
         <v>7</v>
@@ -23031,7 +23031,7 @@
         <v>25</v>
       </c>
       <c r="D332" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E332">
         <v>7</v>
@@ -23067,7 +23067,7 @@
         <v>1</v>
       </c>
       <c r="R332" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S332" t="b">
         <v>1</v>
@@ -23076,7 +23076,7 @@
         <v>7</v>
       </c>
       <c r="U332">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V332">
         <v>7</v>
@@ -23161,7 +23161,7 @@
         <v>25</v>
       </c>
       <c r="D334" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E334">
         <v>7</v>
@@ -23197,7 +23197,7 @@
         <v>1</v>
       </c>
       <c r="R334" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S334" t="b">
         <v>1</v>
@@ -23226,7 +23226,7 @@
         <v>25</v>
       </c>
       <c r="D335" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E335">
         <v>7</v>
@@ -23262,7 +23262,7 @@
         <v>1</v>
       </c>
       <c r="R335" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S335" t="b">
         <v>1</v>
@@ -23271,7 +23271,7 @@
         <v>7</v>
       </c>
       <c r="U335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V335">
         <v>7</v>
@@ -23356,7 +23356,7 @@
         <v>25</v>
       </c>
       <c r="D337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E337">
         <v>7</v>
@@ -23392,7 +23392,7 @@
         <v>1</v>
       </c>
       <c r="R337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S337" t="b">
         <v>1</v>
@@ -23401,7 +23401,7 @@
         <v>7</v>
       </c>
       <c r="U337">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V337">
         <v>7</v>
@@ -23421,7 +23421,7 @@
         <v>25</v>
       </c>
       <c r="D338" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E338">
         <v>7</v>
@@ -23457,7 +23457,7 @@
         <v>1</v>
       </c>
       <c r="R338" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S338" t="b">
         <v>1</v>
@@ -23486,7 +23486,7 @@
         <v>25</v>
       </c>
       <c r="D339" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E339">
         <v>7</v>
@@ -23522,7 +23522,7 @@
         <v>1</v>
       </c>
       <c r="R339" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S339" t="b">
         <v>1</v>
@@ -23551,7 +23551,7 @@
         <v>25</v>
       </c>
       <c r="D340" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E340">
         <v>7</v>
@@ -23587,7 +23587,7 @@
         <v>1</v>
       </c>
       <c r="R340" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S340" t="b">
         <v>1</v>
@@ -23596,7 +23596,7 @@
         <v>7</v>
       </c>
       <c r="U340">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V340">
         <v>7</v>
@@ -23616,7 +23616,7 @@
         <v>25</v>
       </c>
       <c r="D341" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E341">
         <v>7</v>
@@ -23652,7 +23652,7 @@
         <v>1</v>
       </c>
       <c r="R341" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S341" t="b">
         <v>1</v>
@@ -23661,7 +23661,7 @@
         <v>7</v>
       </c>
       <c r="U341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V341">
         <v>7</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
@@ -88,10 +88,10 @@
     <t>cant_min_en_p_elegido</t>
   </si>
   <si>
-    <t>D35_R35_Pentropia</t>
+    <t>PRD35_PR35_CPent_UD080_PE45</t>
   </si>
   <si>
-    <t>D35_R35_Pproporcion</t>
+    <t>PRD35_PR35_CPprop_UD080_Ppp041</t>
   </si>
   <si>
     <t>M</t>
